--- a/Analysis/Hybrid_Ablation/hybrid_ablation_friedman_tests.xlsx
+++ b/Analysis/Hybrid_Ablation/hybrid_ablation_friedman_tests.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,6 +452,16 @@
           <t>n_configs</t>
         </is>
       </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>p_holm</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>significant_holm</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -479,6 +489,12 @@
       <c r="G2" t="n">
         <v>3</v>
       </c>
+      <c r="H2" t="n">
+        <v>7.189751027225631e-18</v>
+      </c>
+      <c r="I2" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -506,6 +522,12 @@
       <c r="G3" t="n">
         <v>3</v>
       </c>
+      <c r="H3" t="n">
+        <v>3.96213819505597e-12</v>
+      </c>
+      <c r="I3" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -533,6 +555,12 @@
       <c r="G4" t="n">
         <v>3</v>
       </c>
+      <c r="H4" t="n">
+        <v>4.847607949025935e-64</v>
+      </c>
+      <c r="I4" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -560,6 +588,12 @@
       <c r="G5" t="n">
         <v>3</v>
       </c>
+      <c r="H5" t="n">
+        <v>5.274615435877817e-20</v>
+      </c>
+      <c r="I5" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -587,6 +621,12 @@
       <c r="G6" t="n">
         <v>3</v>
       </c>
+      <c r="H6" t="n">
+        <v>2.617591371228645e-14</v>
+      </c>
+      <c r="I6" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -614,6 +654,12 @@
       <c r="G7" t="n">
         <v>3</v>
       </c>
+      <c r="H7" t="n">
+        <v>4.46050625730004e-66</v>
+      </c>
+      <c r="I7" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -641,6 +687,12 @@
       <c r="G8" t="n">
         <v>3</v>
       </c>
+      <c r="H8" t="n">
+        <v>1.523890173415963e-18</v>
+      </c>
+      <c r="I8" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -668,6 +720,12 @@
       <c r="G9" t="n">
         <v>3</v>
       </c>
+      <c r="H9" t="n">
+        <v>4.05657205337039e-13</v>
+      </c>
+      <c r="I9" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -694,6 +752,12 @@
       </c>
       <c r="G10" t="n">
         <v>3</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.011816154762527e-61</v>
+      </c>
+      <c r="I10" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/Analysis/Hybrid_Ablation/hybrid_ablation_friedman_tests.xlsx
+++ b/Analysis/Hybrid_Ablation/hybrid_ablation_friedman_tests.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -490,7 +490,7 @@
         <v>3</v>
       </c>
       <c r="H2" t="n">
-        <v>7.189751027225631e-18</v>
+        <v>8.987188784032039e-18</v>
       </c>
       <c r="I2" t="b">
         <v>1</v>
@@ -556,7 +556,7 @@
         <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>4.847607949025935e-64</v>
+        <v>6.059509936282419e-64</v>
       </c>
       <c r="I4" t="b">
         <v>1</v>
@@ -565,7 +565,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -574,22 +574,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>92.36111111111106</v>
+        <v>87.63555555555565</v>
       </c>
       <c r="D5" t="n">
-        <v>8.791025726463029e-21</v>
+        <v>9.33643121289958e-20</v>
       </c>
       <c r="E5" t="n">
         <v>2</v>
       </c>
       <c r="F5" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G5" t="n">
         <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>5.274615435877817e-20</v>
+        <v>6.535501849029706e-19</v>
       </c>
       <c r="I5" t="b">
         <v>1</v>
@@ -598,7 +598,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -607,22 +607,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>64.74509803921543</v>
+        <v>56.82142857142935</v>
       </c>
       <c r="D6" t="n">
-        <v>8.725304570762149e-15</v>
+        <v>4.58546685700187e-13</v>
       </c>
       <c r="E6" t="n">
         <v>2</v>
       </c>
       <c r="F6" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G6" t="n">
         <v>3</v>
       </c>
       <c r="H6" t="n">
-        <v>2.617591371228645e-14</v>
+        <v>9.170933714003739e-13</v>
       </c>
       <c r="I6" t="b">
         <v>1</v>
@@ -631,7 +631,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -640,22 +640,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>305.3451568894954</v>
+        <v>301.7339055793992</v>
       </c>
       <c r="D7" t="n">
-        <v>4.956118063666711e-67</v>
+        <v>3.01519151203287e-66</v>
       </c>
       <c r="E7" t="n">
         <v>2</v>
       </c>
       <c r="F7" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G7" t="n">
         <v>3</v>
       </c>
       <c r="H7" t="n">
-        <v>4.46050625730004e-66</v>
+        <v>3.316710663236157e-65</v>
       </c>
       <c r="I7" t="b">
         <v>1</v>
@@ -664,7 +664,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -673,22 +673,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>85.26940639269388</v>
+        <v>92.36111111111106</v>
       </c>
       <c r="D8" t="n">
-        <v>3.047780346831926e-19</v>
+        <v>8.791025726463029e-21</v>
       </c>
       <c r="E8" t="n">
         <v>2</v>
       </c>
       <c r="F8" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G8" t="n">
         <v>3</v>
       </c>
       <c r="H8" t="n">
-        <v>1.523890173415963e-18</v>
+        <v>7.032820581170423e-20</v>
       </c>
       <c r="I8" t="b">
         <v>1</v>
@@ -697,7 +697,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -706,22 +706,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>58.45283018867858</v>
+        <v>64.74509803921543</v>
       </c>
       <c r="D9" t="n">
-        <v>2.028286026685195e-13</v>
+        <v>8.725304570762149e-15</v>
       </c>
       <c r="E9" t="n">
         <v>2</v>
       </c>
       <c r="F9" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G9" t="n">
         <v>3</v>
       </c>
       <c r="H9" t="n">
-        <v>4.05657205337039e-13</v>
+        <v>3.49012182830486e-14</v>
       </c>
       <c r="I9" t="b">
         <v>1</v>
@@ -730,33 +730,132 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>mae</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>305.3451568894954</v>
+      </c>
+      <c r="D10" t="n">
+        <v>4.956118063666711e-67</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" t="n">
+        <v>194</v>
+      </c>
+      <c r="G10" t="n">
+        <v>3</v>
+      </c>
+      <c r="H10" t="n">
+        <v>5.947341676400053e-66</v>
+      </c>
+      <c r="I10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>qwen</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>kendall_tau</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>85.26940639269388</v>
+      </c>
+      <c r="D11" t="n">
+        <v>3.047780346831926e-19</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F11" t="n">
+        <v>195</v>
+      </c>
+      <c r="G11" t="n">
+        <v>3</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.828668208099156e-18</v>
+      </c>
+      <c r="I11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>top1</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>58.45283018867858</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2.028286026685195e-13</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F12" t="n">
+        <v>195</v>
+      </c>
+      <c r="G12" t="n">
+        <v>3</v>
+      </c>
+      <c r="H12" t="n">
+        <v>6.084858080055585e-13</v>
+      </c>
+      <c r="I12" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
         <is>
           <t>mae</t>
         </is>
       </c>
-      <c r="C10" t="n">
+      <c r="C13" t="n">
         <v>284.7837078651688</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D13" t="n">
         <v>1.445451649660752e-62</v>
       </c>
-      <c r="E10" t="n">
-        <v>2</v>
-      </c>
-      <c r="F10" t="n">
+      <c r="E13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F13" t="n">
         <v>195</v>
       </c>
-      <c r="G10" t="n">
-        <v>3</v>
-      </c>
-      <c r="H10" t="n">
-        <v>1.011816154762527e-61</v>
-      </c>
-      <c r="I10" t="b">
+      <c r="G13" t="n">
+        <v>3</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.300906484694677e-61</v>
+      </c>
+      <c r="I13" t="b">
         <v>1</v>
       </c>
     </row>
